--- a/artfynd/A 13769-2026 artfynd.xlsx
+++ b/artfynd/A 13769-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY74"/>
+  <dimension ref="A1:AZ74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606292</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610331</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610338</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610354</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610355</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610357</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606280</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610470</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606274</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,6 +1742,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606286</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1794,6 +1849,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610264</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610268</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1998,6 +2063,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606291</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2100,6 +2170,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610356</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2202,6 +2277,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606270</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2304,6 +2384,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610335</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2406,6 +2491,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610462</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2508,6 +2598,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606265</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2610,6 +2705,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606266</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2712,6 +2812,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606268</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2814,6 +2919,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606269</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2916,6 +3026,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606272</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3018,6 +3133,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606275</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3120,6 +3240,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606276</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3222,6 +3347,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606279</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3324,6 +3454,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606281</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3426,6 +3561,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606282</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3528,6 +3668,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606283</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3630,6 +3775,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606284</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3732,6 +3882,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606288</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3834,6 +3989,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606289</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3936,6 +4096,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606290</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4038,6 +4203,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610314</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4140,6 +4310,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610320</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4242,6 +4417,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610341</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4344,6 +4524,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610456</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4446,6 +4631,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610458</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4548,6 +4738,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610459</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4650,6 +4845,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610460</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4752,6 +4952,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610461</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4854,6 +5059,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610463</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4956,6 +5166,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610464</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5058,6 +5273,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610471</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5160,6 +5380,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606285</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5262,6 +5487,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610267</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5364,6 +5594,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610311</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5466,6 +5701,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610321</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5568,6 +5808,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610329</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5670,6 +5915,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610344</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5772,6 +6022,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606273</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5874,6 +6129,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610262</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5976,6 +6236,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610317</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6078,6 +6343,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606267</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6180,6 +6450,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606278</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6282,6 +6557,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606293</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6384,6 +6664,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610326</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6486,6 +6771,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610327</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6588,6 +6878,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610337</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6690,6 +6985,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610353</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6792,6 +7092,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606271</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6894,6 +7199,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610308</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6996,6 +7306,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610323</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7098,6 +7413,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610324</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7200,6 +7520,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610334</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7302,6 +7627,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610340</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7404,6 +7734,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610469</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7506,6 +7841,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606277</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7608,6 +7948,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610316</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7710,6 +8055,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610319</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7812,6 +8162,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610330</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7914,6 +8269,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610313</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8016,6 +8376,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610310</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8118,8 +8483,88 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610346</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>